--- a/data_dictionaries/pt-BR/Belvo_Data_Dictionary_pt-BR.xlsx
+++ b/data_dictionaries/pt-BR/Belvo_Data_Dictionary_pt-BR.xlsx
@@ -31566,7 +31566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I123"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -32117,17 +32117,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>tax_details.retained_taxes[].tax</t>
+          <t>tax_details.retained_taxes[].tax_type</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>O tipo de imposto retido (por exemplo, ISR, IVA ou IEPS).</t>
+          <t>O código do tipo de imposto para este imposto retido, conforme definido pela entidade legal no país.</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>Tasa</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -32143,7 +32143,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -32152,25 +32152,25 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>tax_details.retained_taxes[].tax_percentage</t>
+          <t>tax_details.retained_taxes[].tax</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>A porcentagem de imposto retido.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
+          <t>O tipo de imposto retido (por exemplo, ISR, IVA ou IEPS).</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>ISR</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -32178,7 +32178,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -32187,12 +32187,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>tax_details.retained_taxes[].pre_tax_amount</t>
+          <t>tax_details.retained_taxes[].tax_percentage</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>O valor antes dos impostos.</t>
+          <t>A porcentagem de imposto retido.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
@@ -32222,19 +32222,15 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>tax_details.retained_taxes[].tax_amount</t>
+          <t>tax_details.retained_taxes[].pre_tax_amount</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>O valor do imposto retido.</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
+          <t>O valor antes dos impostos.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
           <t>number</t>
@@ -32252,7 +32248,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -32261,21 +32257,29 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>tax_details.transferred_taxes</t>
+          <t>tax_details.retained_taxes[].tax_amount</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Lista de impostos transferidos.</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr"/>
+          <t>O valor do imposto retido.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -32292,22 +32296,18 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>tax_details.transferred_taxes[].tax</t>
+          <t>tax_details.transferred_taxes</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>O tipo de imposto transferido (por exemplo, ISR, IVA ou IEPS).</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>IVA</t>
-        </is>
-      </c>
+          <t>Lista de impostos transferidos.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -32327,29 +32327,25 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>tax_details.transferred_taxes[].tax_percentage</t>
+          <t>tax_details.transferred_taxes[].tax_type</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>A porcentagem de imposto transferido.</t>
+          <t>O código do tipo de imposto (TipoFactor) para este imposto transferido, conforme definido pela entidade legal no país.</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Tasa</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -32357,7 +32353,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -32366,29 +32362,25 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>tax_details.transferred_taxes[].pre_tax_amount</t>
+          <t>tax_details.transferred_taxes[].tax</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>O valor antes dos impostos.</t>
+          <t>O tipo de imposto transferido (por exemplo, ISR, IVA ou IEPS).</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>IVA</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -32405,17 +32397,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>tax_details.transferred_taxes[].tax_amount</t>
+          <t>tax_details.transferred_taxes[].tax_percentage</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>O valor do imposto transferido.</t>
+          <t>A porcentagem de imposto transferido.</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>150.4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -32444,33 +32436,37 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>sender_id</t>
+          <t>tax_details.transferred_taxes[].pre_tax_amount</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>O ID fiscal do remetente da fatura</t>
+          <t>O valor antes dos impostos.</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>AAA111111AA11</t>
+          <t>940</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -32479,25 +32475,29 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>sender_fiscal_regime</t>
+          <t>tax_details.transferred_taxes[].tax_amount</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>O regime tributário do remetente, conforme definido pela pessoa jurídica no país.</t>
+          <t>O valor do imposto transferido.</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>150.4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -32505,7 +32505,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -32514,17 +32514,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>sender_name</t>
+          <t>sender_id</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>O nome do remetente da fatura.</t>
+          <t>O ID fiscal do remetente da fatura</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ACME CORP</t>
+          <t>AAA111111AA11</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -32549,10 +32549,80 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>sender_fiscal_regime</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>O regime tributário do remetente, conforme definido pela pessoa jurídica no país.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>sender_name</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>O nome do remetente da fatura.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>ACME CORP</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>sender_tax_fraud_status</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Indica se o remetente está ou não na lista de fraude fiscal do SAT por ter enviado dados incorretos, ter pagamentos pendentes ou ter realizado negócios que violam os regulamentos da instituição fiscal.&lt;br&gt;&lt;br&gt;
 O SAT atualiza a lista de fraude fiscal a cada três meses. &lt;br&gt;&lt;br&gt;
@@ -32575,79 +32645,9 @@
 O receptor ou remetente não é encontrado na lista (ou seja, está em conformidade com os regulamentos da instituição fiscal).</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>NO_TAX_FRAUD_STATUS</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>receiver_id</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>O ID fiscal do destinatário da fatura.</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>BBB222222BB22</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>receiver_postal_code</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>O código postal do destinatário.</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>11560</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -32663,7 +32663,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -32672,17 +32672,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>receiver_fiscal_regime</t>
+          <t>receiver_id</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>O regime tributário do recebedor, conforme definido pela pessoa jurídica no país.</t>
+          <t>O ID fiscal do destinatário da fatura.</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>BBB222222BB22</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -32693,7 +32693,7 @@
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -32707,17 +32707,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>receiver_name</t>
+          <t>receiver_postal_code</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>O nome do destinatário da fatura.</t>
+          <t>O código postal do destinatário.</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>BELVO CORP</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -32728,12 +32728,12 @@
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -32742,10 +32742,80 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>receiver_fiscal_regime</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>O regime tributário do recebedor, conforme definido pela pessoa jurídica no país.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>receiver_name</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>O nome do destinatário da fatura.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>BELVO CORP</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>receiver_tax_fraud_status</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Indica se o destinatário está ou não na lista de fraude fiscal do SAT por ter enviado dados incorretos, ter pagamentos pendentes ou ter realizado negócios que violam os regulamentos da instituição fiscal.&lt;br&gt;&lt;br&gt;
 O SAT atualiza a lista de fraude fiscal a cada três meses. &lt;br&gt;&lt;br&gt;
@@ -32768,90 +32838,20 @@
 O destinatário ou remetente não é encontrado na lista (ou seja, está em conformidade com os regulamentos da instituição fiscal).</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>NO_TAX_FRAUD_STATUS</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>cancelation_status</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Se a fatura for cancelada, este campo indica o status do cancelamento.</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>cancelation_update_date</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>A data do cancelamento da fatura, no formato `YYYY-MM-DD`.</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>2019-12-02</t>
-        </is>
-      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -32865,29 +32865,21 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>certification_date</t>
+          <t>cancelation_status</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>A data da certificação fiscal, no formato `YYYY-MM-DD`.</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>2019-12-01</t>
-        </is>
-      </c>
+          <t>Se a fatura for cancelada, este campo indica o status do cancelamento.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -32904,17 +32896,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>certification_authority</t>
+          <t>cancelation_update_date</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>O ID fiscal do provedor de certificação.</t>
+          <t>A data do cancelamento da fatura, no formato `YYYY-MM-DD`.</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>CCC333333CC33</t>
+          <t>2019-12-02</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -32922,7 +32914,11 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -32939,227 +32935,231 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>certification_date</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>A data da certificação fiscal, no formato `YYYY-MM-DD`.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>certification_authority</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>O ID fiscal do provedor de certificação.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>CCC333333CC33</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>payment_type</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>O código do tipo de pagamento usado para esta fatura, conforme definido pela entidade legal do país.
 - 🇲🇽 México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payment-type" target="_blank"&gt;Artigo de referência do catálogo SAT&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>payment_type_description</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>*Este campo foi descontinuado. Para mais informações sobre a Belvo e descontinuação, consulte nossa explicação sobre Campos descontinuados.*</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>payment_method</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>O código do método de pagamento usado para esta fatura, conforme definido pela entidade legal do país.
 - 🇲🇽 México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payment-method" target="_blank"&gt;artigo de referência do catálogo SAT&lt;/a&gt;. Para o México, retornamos `PUE`, `PPD` ou `null`.</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>PUE</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>PUE, PPD, None</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>payment_method_description</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>*Este campo foi descontinuado. Para mais informações sobre a Belvo e descontinuação, consulte nossa explicação sobre Campos descontinuados.*
 *A descrição do método de pagamento utilizado para esta fatura.*</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>usage</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>O código de uso da fatura, conforme definido pela entidade legal do país.
 - 🇲🇽 México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#usage" target="_blank"&gt;artigo de referência do catálogo SAT&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>P01</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>A versão CFDI da fatura.</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>place_of_issue</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>O código postal de onde a fatura foi emitida.</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>01165</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -33184,29 +33184,33 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>invoice_details</t>
+          <t>version</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Uma lista de descrições para cada item (produto comprado ou serviço prestado) na fatura.</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
+          <t>A versão CFDI da fatura.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -33215,17 +33219,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].collected_at</t>
+          <t>place_of_issue</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>O carimbo de data/hora ISO-8601 quando o ponto de dados foi coletado.</t>
+          <t>O código postal de onde a fatura foi emitida.</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2022-02-09T08:45:50.406032Z</t>
+          <t>01165</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -33233,11 +33237,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
+      <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -33245,7 +33245,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -33254,22 +33254,18 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].description</t>
+          <t>invoice_details</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>A descrição do item da fatura (uma fatura pode ter um ou mais itens).</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>December 2019 accounting fees</t>
-        </is>
-      </c>
+          <t>Uma lista de descrições para cada item (produto comprado ou serviço prestado) na fatura.</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -33280,7 +33276,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -33289,17 +33285,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].product_identification</t>
+          <t>invoice_details[].collected_at</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>O código de identificação do produto ou serviço, conforme definido pela entidade legal no país.\n- \U0001F1F2\U0001F1FD &lt;a href="http://200.57.3.89/Pys/catPyS.aspx" target="_blank"&gt;México&lt;/a&gt;.</t>
+          <t>O carimbo de data/hora ISO-8601 quando o ponto de dados foi coletado.</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>84101600</t>
+          <t>2022-02-09T08:45:50.406032Z</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -33307,15 +33303,19 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -33324,29 +33324,25 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].quantity</t>
+          <t>invoice_details[].description</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>A quantidade deste item da fatura.</t>
+          <t>A descrição do item da fatura (uma fatura pode ter um ou mais itens).</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>December 2019 accounting fees</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -33363,17 +33359,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].unit_code</t>
+          <t>invoice_details[].product_identification</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>A unidade de medida, conforme definida pela entidade legal no país. \n- \U0001F1F2\U0001F1FD México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#unit-code" target="_blank"&gt;referência do catálogo SAT&lt;/a&gt;.</t>
+          <t>O código de identificação do produto ou serviço, conforme definido pela entidade legal no país.\n- \U0001F1F2\U0001F1FD &lt;a href="http://200.57.3.89/Pys/catPyS.aspx" target="_blank"&gt;México&lt;/a&gt;.</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>E48</t>
+          <t>84101600</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -33398,25 +33394,29 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].unit_description</t>
+          <t>invoice_details[].quantity</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>A descrição do item, conforme definido pela entidade legal no país.\n- \U0001F1F2\U0001F1FD México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#unit-code" target="_blank"&gt;referência do catálogo SAT&lt;/a&gt;.</t>
+          <t>A quantidade deste item da fatura.</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Unidad de servicio</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -33433,29 +33433,25 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].unit_amount</t>
+          <t>invoice_details[].unit_code</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>O preço de um único item.</t>
+          <t>A unidade de medida, conforme definida pela entidade legal no país. \n- \U0001F1F2\U0001F1FD México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#unit-code" target="_blank"&gt;referência do catálogo SAT&lt;/a&gt;.</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>E48</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -33472,15 +33468,19 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].tax_type</t>
+          <t>invoice_details[].unit_description</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>O tipo de imposto do item.</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr"/>
+          <t>A descrição do item, conforme definido pela entidade legal no país.\n- \U0001F1F2\U0001F1FD México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#unit-code" target="_blank"&gt;referência do catálogo SAT&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Unidad de servicio</t>
+        </is>
+      </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -33489,7 +33489,7 @@
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -33503,17 +33503,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].pre_tax_amount</t>
+          <t>invoice_details[].unit_amount</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>O preço total deste item antes da aplicação de impostos é (`quantity` x `unit_amount`).</t>
+          <t>O preço de um único item.</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -33542,17 +33542,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].tax_percentage</t>
+          <t>invoice_details[].discount</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>A porcentagem de imposto a ser aplicada.</t>
+          <t>O valor do desconto aplicado a este item da fatura.</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -33567,7 +33567,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -33581,32 +33581,28 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].tax_amount</t>
+          <t>invoice_details[].tax_subject_code</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>O valor do imposto para este item da fatura (`pre_tax_amount` x `tax_percentage`).</t>
+          <t>Indica a que imposto este item está sujeito, conforme definido pela entidade legal no país.</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -33620,32 +33616,28 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].total_amount</t>
+          <t>invoice_details[].identifier_number</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>O preço total para este item da fatura (`pre_tax_amount` + `tax_amount`).</t>
+          <t>O número de identificação do item, conforme definido pelo vendedor. Isso pode ser usado para identificar o produto ou serviço no sistema do vendedor.</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>PROD-12345</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -33659,29 +33651,37 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].retained_taxes</t>
+          <t>invoice_details[].pre_tax_amount</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>O imposto retido no item da fatura.</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr"/>
+          <t>O preço total deste item antes da aplicação de impostos é (`quantity` x `unit_amount`).</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -33690,37 +33690,37 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].retained_taxes[].collected_at</t>
+          <t>invoice_details[].tax_percentage</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>O carimbo de data/hora ISO-8601 quando o ponto de dados foi coletado.</t>
+          <t>A porcentagem de imposto a ser aplicada.</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>2022-02-09T08:45:50.406032Z</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>date-time</t>
+          <t>float</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -33729,25 +33729,29 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].retained_taxes[].tax</t>
+          <t>invoice_details[].tax_amount</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>O tipo de imposto retido (por exemplo, ISR, IVA ou IEPS).</t>
+          <t>O valor do imposto para este item da fatura (`pre_tax_amount` x `tax_percentage`).</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -33764,17 +33768,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].retained_taxes[].tax_percentage</t>
+          <t>invoice_details[].total_amount</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>A porcentagem de imposto retido.</t>
+          <t>O preço total para este item da fatura (`pre_tax_amount` + `tax_amount`).</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>464</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -33803,37 +33807,29 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].retained_taxes[].retained_tax_amount</t>
+          <t>invoice_details[].retained_taxes</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>O valor do imposto retido.</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>209.79</t>
-        </is>
-      </c>
+          <t>O imposto retido no item da fatura.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -33842,21 +33838,29 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].transferred_taxes</t>
+          <t>invoice_details[].retained_taxes[].collected_at</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Os impostos transferidos relacionados à fatura.</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr"/>
+          <t>O carimbo de data/hora ISO-8601 quando o ponto de dados foi coletado.</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-09T08:45:50.406032Z</t>
+        </is>
+      </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -33873,17 +33877,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].transferred_taxes[].collected_at</t>
+          <t>invoice_details[].retained_taxes[].tax_type</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>O carimbo de data/hora ISO-8601 quando o ponto de dados foi coletado.</t>
+          <t>O código do tipo de imposto para este imposto retido, conforme definido pela entidade legal no país.</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2022-02-09T08:45:50.406032Z</t>
+          <t>Tasa</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -33891,11 +33895,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
+      <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -33903,7 +33903,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -33912,17 +33912,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].transferred_taxes[].tax</t>
+          <t>invoice_details[].retained_taxes[].tax</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>O tipo de imposto transferido (por exemplo, ISR, IVA ou IEPS).</t>
+          <t>O tipo de imposto retido (por exemplo, ISR, IVA ou IEPS).</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>IVA</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -33947,12 +33947,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].transferred_taxes[].tax_percentage</t>
+          <t>invoice_details[].retained_taxes[].tax_percentage</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>A porcentagem de imposto transferido.</t>
+          <t>A porcentagem de imposto retido.</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -33986,12 +33986,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].transferred_taxes[].transferred_tax_amount</t>
+          <t>invoice_details[].retained_taxes[].retained_tax_amount</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>O valor do imposto transferido.</t>
+          <t>O valor do imposto retido.</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -34025,10 +34025,228 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>invoice_details[].transferred_taxes</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Os impostos transferidos relacionados à fatura.</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>invoice_details[].transferred_taxes[].collected_at</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>O carimbo de data/hora ISO-8601 quando o ponto de dados foi coletado.</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-09T08:45:50.406032Z</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>invoice_details[].transferred_taxes[].tax_type</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>O código do tipo de imposto para este imposto transferido, conforme definido pela entidade legal no país.</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Tasa</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>invoice_details[].transferred_taxes[].tax</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>O tipo de imposto transferido (por exemplo, ISR, IVA ou IEPS).</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>invoice_details[].transferred_taxes[].tax_percentage</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>A porcentagem de imposto transferido.</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>invoice_details[].transferred_taxes[].transferred_tax_amount</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>O valor do imposto transferido.</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>209.79</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>A moeda da fatura. Por exemplo:
 - 🇧🇷 BRL (Real Brasileiro)
@@ -34037,251 +34255,25 @@
 - 🇺🇸 USD (Dólar dos Estados Unidos)</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>MXN</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>subtotal_amount</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>O valor antes dos impostos desta fatura (soma do `pre_tax_amount` de cada item).</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>exchange_rate</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>A taxa de câmbio utilizada nesta fatura para a moeda.</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>0.052</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>tax_amount</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>O valor do imposto para esta fatura (soma do `tax_amount` de cada item).</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>discount_amount</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>O valor total descontado nesta fatura.</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>total_amount</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>O valor total da fatura (`subtotal_amount` + `tax_amount` - `discount_amount`)</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>related_invoices</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Uma lista de faturas relacionadas.</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -34290,28 +34282,32 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>related_invoices[].relationship_type</t>
+          <t>subtotal_amount</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>O tipo de relação entre esta fatura e a fatura relacionada, conforme definido pela entidade legal no país. Para mais informações, consulte nosso &lt;a href="https://developers.belvo.com/docs/sat-catalogs#related-invoices" target="_blank"&gt;artigo de referência do catálogo SAT&lt;/a&gt;.</t>
+          <t>O valor antes dos impostos desta fatura (soma do `pre_tax_amount` de cada item).</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -34325,28 +34321,32 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>related_invoices[].related_invoice_identification</t>
+          <t>exchange_rate</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>O ID SAT da nota fiscal relacionada.</t>
+          <t>A taxa de câmbio utilizada nesta fatura para a moeda.</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>INV-123456</t>
+          <t>0.052</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -34360,21 +34360,29 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>tax_amount</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Uma lista detalhando todos os pagamentos de faturas.</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr"/>
+          <t>O valor do imposto para esta fatura (soma do `tax_amount` de cada item).</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -34382,7 +34390,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -34391,27 +34399,27 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>payments[].date</t>
+          <t>discount_amount</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Carimbo de data/hora ISO-8601 quando o pagamento foi realizado.</t>
+          <t>O valor total descontado nesta fatura.</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>2020-03-17T12:00:00.000Z</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>date-time</t>
+          <t>float</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -34430,46 +34438,256 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>O valor total da fatura (`subtotal_amount` + `tax_amount` - `discount_amount`)</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>related_invoices</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Uma lista de faturas relacionadas.</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>related_invoices[].relationship_type</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>O tipo de relação entre esta fatura e a fatura relacionada, conforme definido pela entidade legal no país. Para mais informações, consulte nosso &lt;a href="https://developers.belvo.com/docs/sat-catalogs#related-invoices" target="_blank"&gt;artigo de referência do catálogo SAT&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>related_invoices[].related_invoice_identification</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>O ID SAT da nota fiscal relacionada.</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>INV-123456</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>payments</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Uma lista detalhando todos os pagamentos de faturas.</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>payments[].date</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Carimbo de data/hora ISO-8601 quando o pagamento foi realizado.</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>2020-03-17T12:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
           <t>payments[].payment_type</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Código do tipo de pagamento usado para esta fatura, conforme definido pela entidade legal do país.
 - 🇲🇽 México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payment-type" target="_blank"&gt;artigo de referência do catálogo SAT&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>payments[].currency</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>A moeda do pagamento. Por exemplo:
 - 🇧🇷 BRL (Real Brasileiro)
@@ -34478,223 +34696,9 @@
 Por favor, note que outras moedas além das listadas acima podem ser retornadas.</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>BRL</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>payments[].exchange_rate</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>A taxa de câmbio de `currency` para MXN no momento em que o pagamento foi realizado.</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>payments[].amount</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>O valor da fatura, na moeda da fatura original.</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>8000.5</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>payments[].operation_number</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>O identificador interno da instituição fiscal para a operação.</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>831840</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>payments[].beneficiary_rfc</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>O ID fiscal do beneficiário do pagamento.</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>BNM840515VB1</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>payments[].beneficiary_account_number</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>O número da conta bancária do beneficiário do pagamento.</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>12343453245633</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>payments[].payer_rfc</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>O ID fiscal do emissor do pagamento.</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>BKJM840515VB1</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -34719,17 +34723,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>payments[].payer_account_number</t>
+          <t>payments[].exchange_rate</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>O número da conta bancária do emissor do pagamento.</t>
+          <t>A taxa de câmbio de `currency` para MXN no momento em que o pagamento foi realizado.</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>13343663245699</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -34754,25 +34758,29 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>payments[].payer_bank_name</t>
+          <t>payments[].amount</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>A instituição bancária que foi utilizada pelo emissor do pagamento.</t>
+          <t>O valor da fatura, na moeda da fatura original.</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>CITI BANAMEX</t>
+          <t>8000.5</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -34789,18 +34797,22 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>payments[].related_documents</t>
+          <t>payments[].operation_number</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Uma lista de todas as faturas diferidas relacionadas afetadas pelo pagamento.</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr"/>
+          <t>O identificador interno da instituição fiscal para a operação.</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>831840</t>
+        </is>
+      </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -34811,7 +34823,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
@@ -34820,17 +34832,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>payments[].related_documents[].invoice_identification</t>
+          <t>payments[].beneficiary_rfc</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>O ID exclusivo da instituição fiscal para a fatura diferida relacionada.</t>
+          <t>O ID fiscal do beneficiário do pagamento.</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>7EE015F3-6311-11EA-B02A-00155D014007</t>
+          <t>BNM840515VB1</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -34841,7 +34853,7 @@
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -34855,10 +34867,216 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>payments[].beneficiary_account_number</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>O número da conta bancária do beneficiário do pagamento.</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>12343453245633</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>payments[].payer_rfc</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>O ID fiscal do emissor do pagamento.</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>BKJM840515VB1</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>payments[].payer_account_number</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>O número da conta bancária do emissor do pagamento.</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>13343663245699</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>payments[].payer_bank_name</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>A instituição bancária que foi utilizada pelo emissor do pagamento.</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>CITI BANAMEX</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>payments[].related_documents</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Uma lista de todas as faturas diferidas relacionadas afetadas pelo pagamento.</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr"/>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>payments[].related_documents[].invoice_identification</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>O ID exclusivo da instituição fiscal para a fatura diferida relacionada.</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>7EE015F3-6311-11EA-B02A-00155D014007</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>payments[].related_documents[].currency</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>A moeda da fatura relacionada. Por exemplo:
 - 🇧🇷 BRL (Real Brasileiro)
@@ -34867,236 +35085,14 @@
 Por favor, note que outras moedas além das listadas acima podem ser retornadas.</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>MXN</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>payments[].related_documents[].payment_method</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>O método de pagamento da fatura relacionada.</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>PPD</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>payments[].related_documents[].partiality_number</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>O número da parcela de pagamento.</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>payments[].related_documents[].previous_balance</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>O valor da fatura antes do pagamento.</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>18877.84</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>payments[].related_documents[].amount_paid</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>O valor pago nesta parcela.</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>payments[].related_documents[].outstanding_balance</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>O valor restante a ser pago.</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>10877.84</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>payroll</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Detalhes sobre o pagamento da folha de pagamento. Aplicável apenas para faturas de folha de pagamento.</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr"/>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -35116,29 +35112,25 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>payroll.days</t>
+          <t>payments[].related_documents[].payment_method</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>O número de dias cobertos pelo pagamento.</t>
+          <t>O método de pagamento da fatura relacionada.</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>PPD</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -35155,256 +35147,252 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>payments[].related_documents[].partiality_number</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>O número da parcela de pagamento.</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>payments[].related_documents[].previous_balance</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>O valor da fatura antes do pagamento.</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>18877.84</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>payments[].related_documents[].amount_paid</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>O valor pago nesta parcela.</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>payments[].related_documents[].outstanding_balance</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>O valor restante a ser pago.</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>10877.84</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>payroll</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Detalhes sobre o pagamento da folha de pagamento. Aplicável apenas para faturas de folha de pagamento.</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr"/>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>payroll.days</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>O número de dias cobertos pelo pagamento.</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
           <t>payroll.type</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>O tipo de folha de pagamento, conforme definido pela entidade legal do país.
 - 🇲🇽 México &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-type" target="_blank"&gt;artigo de referência do catálogo SAT&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>payroll.amount</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>O valor total do pagamento da folha de pagamento.</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>20400.1</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>payroll.version</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>A versão do objeto de folha de pagamento.</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>payroll.date_from</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>A data de início do período de pagamento, no formato `YYYY-MM-DD`.</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>2018-07-01</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>payroll.date_to</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>A data de término do período de pagamento, no formato `YYYY-MM-DD`.</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>2018-07-31</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>payroll.collected_at</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>O carimbo de data/hora ISO-8601 quando o ponto de dados foi coletado.</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>2022-02-09T08:45:50.406032Z</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>payroll.payment_date</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>A data de pagamento, no formato `YYYY-MM-DD`.</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>2018-07-16</t>
-        </is>
-      </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+      <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -35412,7 +35400,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -35421,10 +35409,240 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>payroll.amount</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>O valor total do pagamento da folha de pagamento.</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>20400.1</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>payroll.version</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>A versão do objeto de folha de pagamento.</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>payroll.date_from</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>A data de início do período de pagamento, no formato `YYYY-MM-DD`.</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>payroll.date_to</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>A data de término do período de pagamento, no formato `YYYY-MM-DD`.</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>2018-07-31</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>payroll.collected_at</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>O carimbo de data/hora ISO-8601 quando o ponto de dados foi coletado.</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-09T08:45:50.406032Z</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>payroll.payment_date</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>A data de pagamento, no formato `YYYY-MM-DD`.</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>2018-07-16</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
           <t>payroll.periodicity</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Com que frequência o pagamento da folha de pagamento é realizado.
 Para o SAT do México, retornamos um dos seguintes valores:
@@ -35441,223 +35659,9 @@
   - `OTHER_PERIODICITY`</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>MONTHLY</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr"/>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>DAILY, WEEKLY, TENTH_DAY, FOURTEENTH_DAY, FIFTEENTH_DAY, MONTHLY, BIMONTHLY, PER_TASK, COMMISSION, ONE_OFF, OTHER_PERIODICITY, null</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>payroll.earnings_breakdown</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Uma análise detalhada dos ganhos para o pagamento da folha de pagamento.</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr"/>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr"/>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>payroll.earnings_breakdown[].type</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>O tipo de renda. Para uma lista completa de valores possíveis, consulte a &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-earnings-breakdown-type" target="_blank"&gt;tabela de tipos de detalhamento de ganhos da folha de pagamento&lt;/a&gt;.</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>CHRISTMAS_BONUS</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>payroll.earnings_breakdown[].taxable_amount</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>O valor da renda que é tributável.</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>payroll.earnings_breakdown[].vat_free_amount</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>O valor da receita que não está sujeito ao IVA.</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>payroll.tax_deductions</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Uma análise das deduções fiscais no pagamento da folha de pagamento.</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr"/>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr"/>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>payroll.tax_deductions[].type</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>O tipo de dedução fiscal. Para uma lista completa de valores possíveis, consulte a &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-tax-deductions-type" target="_blank"&gt;tabela de tipos de deduções fiscais de folha de pagamento&lt;/a&gt;.</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>UNION_FEES</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -35676,35 +35680,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>DAILY, WEEKLY, TENTH_DAY, FOURTEENTH_DAY, FIFTEENTH_DAY, MONTHLY, BIMONTHLY, PER_TASK, COMMISSION, ONE_OFF, OTHER_PERIODICITY, null</t>
+        </is>
+      </c>
       <c r="I111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>payroll.tax_deductions[].amount</t>
+          <t>payroll.earnings_breakdown</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>O valor da dedução fiscal.</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
-      </c>
+          <t>Uma análise detalhada dos ganhos para o pagamento da folha de pagamento.</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr"/>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -35712,7 +35712,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr"/>
@@ -35721,18 +35721,22 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>payroll.other_payments</t>
+          <t>payroll.earnings_breakdown[].type</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Uma análise detalhada de outros pagamentos para a folha de pagamento.</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr"/>
+          <t>O tipo de renda. Para uma lista completa de valores possíveis, consulte a &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-earnings-breakdown-type" target="_blank"&gt;tabela de tipos de detalhamento de ganhos da folha de pagamento&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>CHRISTMAS_BONUS</t>
+        </is>
+      </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -35752,25 +35756,29 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>payroll.other_payments[].type</t>
+          <t>payroll.earnings_breakdown[].taxable_amount</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>O tipo de outro pagamento. Para uma lista completa de valores possíveis, consulte a &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-other-payments-type" target="_blank"&gt;tabela de tipos de outros pagamentos de folha de pagamento&lt;/a&gt;.</t>
+          <t>O valor da renda que é tributável.</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>EMPLOYMENT_SUBSIDY</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -35778,7 +35786,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr"/>
@@ -35787,17 +35795,17 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>payroll.other_payments[].amount</t>
+          <t>payroll.earnings_breakdown[].vat_free_amount</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>O valor do outro pagamento.</t>
+          <t>O valor da receita que não está sujeito ao IVA.</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -35826,22 +35834,18 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>folio</t>
+          <t>payroll.tax_deductions</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>O número de controle interno que o contribuinte atribui à nota fiscal.</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>Uma análise das deduções fiscais no pagamento da folha de pagamento.</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr"/>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -35861,17 +35865,17 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>export_type</t>
+          <t>payroll.tax_deductions[].type</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>O tipo de exportação da fatura, conforme definido pela entidade legal no país. Para mais informações, consulte nosso &lt;a href="https://developers.belvo.com/docs/sat-catalogs#export-type" target="_blank"&gt;artigo de referência do catálogo SAT&lt;/a&gt;.</t>
+          <t>O tipo de dedução fiscal. Para uma lista completa de valores possíveis, consulte a &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-tax-deductions-type" target="_blank"&gt;tabela de tipos de deduções fiscais de folha de pagamento&lt;/a&gt;.</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>UNION_FEES</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -35896,21 +35900,29 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>xml</t>
+          <t>payroll.tax_deductions[].amount</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>XML do documento da fatura.</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr"/>
+          <t>O valor da dedução fiscal.</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -35918,7 +35930,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
@@ -35927,18 +35939,18 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>payroll.other_payments</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Objeto contendo informações sobre quaisquer avisos relacionados a esta fatura.</t>
+          <t>Uma análise detalhada de outros pagamentos para a folha de pagamento.</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr"/>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -35958,10 +35970,251 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>payroll.other_payments[].type</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>O tipo de outro pagamento. Para uma lista completa de valores possíveis, consulte a &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-other-payments-type" target="_blank"&gt;tabela de tipos de outros pagamentos de folha de pagamento&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>EMPLOYMENT_SUBSIDY</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>payroll.other_payments[].amount</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>O valor do outro pagamento.</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>folio</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>O número de controle interno que o contribuinte atribui à nota fiscal.</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>A série da fatura, conforme definido pelo contribuinte. Este é um campo opcional usado para agrupar faturas.</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>export_type</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>O tipo de exportação da fatura, conforme definido pela entidade legal no país. Para mais informações, consulte nosso &lt;a href="https://developers.belvo.com/docs/sat-catalogs#export-type" target="_blank"&gt;artigo de referência do catálogo SAT&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>xml</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>XML do documento da fatura.</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr"/>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Objeto contendo informações sobre quaisquer avisos relacionados a esta fatura.</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr"/>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
           <t>warnings.code</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>O código de aviso. Pode ser um dos seguintes:
   - `sat_xml_limit_reached`
@@ -35969,37 +36222,37 @@
   - `null`</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>sat_xml_limit_reached</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr"/>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>warnings.message</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>A descrição do aviso.
 A mensagem dependerá do código de aviso:
@@ -36009,7 +36262,7 @@
 O download dos detalhes das notas fiscais não está disponível. O portal do SAT retornou um erro 503.</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The daily limit for XML downloads set by SAT was reached so this invoice
 might be missing data. Please check https://tinyurl.com/yydzhy5d for more
@@ -36017,88 +36270,88 @@
 </t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr"/>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr"/>
-      <c r="I121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>sender_blacklist_status</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>*Este campo foi descontinuado. Para mais informações sobre a Belvo e descontinuação, consulte nossa explicação sobre Campos descontinuados.*
 Por favor, use `sender_tax_fraud_status` em vez disso.</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr"/>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr"/>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr"/>
-      <c r="I122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr"/>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>receiver_blacklist_status</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>*Este campo foi descontinuado. Para mais informações sobre a Belvo e descontinuação, consulte nossa explicação sobre Campos descontinuados.*
 Por favor, use `receiver_tax_fraud_status` em vez disso.</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr"/>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr"/>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr"/>
-      <c r="I123" s="2" t="inlineStr"/>
+      <c r="C130" s="2" t="inlineStr"/>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data_dictionaries/pt-BR/Belvo_Data_Dictionary_pt-BR.xlsx
+++ b/data_dictionaries/pt-BR/Belvo_Data_Dictionary_pt-BR.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -871,14 +871,18 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>form_fields</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr"/>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Este campo está **obsoleto** e será removido em uma versão futura. Por favor, use o campo `id` em vez disso, que é o identificador único para a instituição.</t>
+        </is>
+      </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -889,7 +893,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -898,22 +902,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].name</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>O campo de nome de usuário, senha ou tipo de nome de usuário.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>username</t>
-        </is>
-      </c>
+          <t>form_fields</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -933,17 +929,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].type</t>
+          <t>form_fields[].name</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>O tipo de entrada para o campo do formulário. Por exemplo, string.</t>
+          <t>O campo de nome de usuário, senha ou tipo de nome de usuário.</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>username</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -968,10 +964,45 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>form_fields[].type</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>O tipo de entrada para o campo do formulário. Por exemplo, string.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>form_fields[].label</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>O rótulo do campo do formulário. Por exemplo:
 - Número do cliente
@@ -979,44 +1010,9 @@
 - Documento</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Client number</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>form_fields[].validation</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>O tipo de validação de entrada usado para o campo.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>^.{1,}$</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1041,17 +1037,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].placeholder</t>
+          <t>form_fields[].validation</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>O texto do espaço reservado no campo do formulário.</t>
+          <t>O tipo de validação de entrada usado para o campo.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ABC333333A33</t>
+          <t>^.{1,}$</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1076,17 +1072,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].validation_message</t>
+          <t>form_fields[].placeholder</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>A mensagem exibida quando uma entrada inválida é fornecida no campo do formulário.</t>
+          <t>O texto do espaço reservado no campo do formulário.</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Invalid client number</t>
+          <t>ABC333333A33</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1111,18 +1107,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].values</t>
+          <t>form_fields[].validation_message</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Se o campo do formulário for para documentos, a instituição pode exigir informações adicionais sobre o tipo de documento.</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr"/>
+          <t>A mensagem exibida quando uma entrada inválida é fornecida no campo do formulário.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Invalid client number</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1142,22 +1142,18 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].values[].code</t>
+          <t>form_fields[].values</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>O código do documento.</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
+          <t>Se o campo do formulário for para documentos, a instituição pode exigir informações adicionais sobre o tipo de documento.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1177,10 +1173,45 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>form_fields[].values[].code</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>O código do documento.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>form_fields[].values[].label</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>O rótulo para o campo. Por exemplo:
 - Cédula de Ciudadanía
@@ -1188,44 +1219,9 @@
 - Pasaporte</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Cédula de Ciudadanía</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>form_fields[].values[].validation</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>O tipo de validação de entrada usado para o campo.</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>^.{1,}$</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1250,17 +1246,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].values[].validation_message</t>
+          <t>form_fields[].values[].validation</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>A mensagem exibida quando uma entrada inválida é fornecida no campo do formulário.</t>
+          <t>O tipo de validação de entrada usado para o campo.</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Invalid document number</t>
+          <t>^.{1,}$</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1285,17 +1281,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].values[].placeholder</t>
+          <t>form_fields[].values[].validation_message</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>O texto do espaço reservado no campo do formulário.</t>
+          <t>A mensagem exibida quando uma entrada inválida é fornecida no campo do formulário.</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>DEF4444908M22</t>
+          <t>Invalid document number</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1320,55 +1316,55 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>form_fields[].values[].placeholder</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>O texto do espaço reservado no campo do formulário.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>DEF4444908M22</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>features</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Os recursos que a instituição suporta. Se a instituição não tiver recursos especiais, a Belvo retorna um array vazio.
 Aqui está uma lista dos recursos disponíveis:
 - `token_required` indica que a instituição pode exigir um token durante a criação do link ou ao fazer qualquer outra solicitação.</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr"/>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>array</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>features[].name</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>O nome do recurso.</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>token_required</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1388,17 +1384,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>features[].description</t>
+          <t>features[].name</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>A descrição do recurso.</t>
+          <t>O nome do recurso.</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>The institution may require a token during link creation or login</t>
+          <t>token_required</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1423,10 +1419,45 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>features[].description</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>A descrição do recurso.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>The institution may require a token during link creation or login</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>resources</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Uma lista de recursos do Belvo que você pode usar com a instituição. Esta lista inclui um ou mais dos seguintes recursos:
   - `ACCOUNTS`
@@ -1449,85 +1480,46 @@
   - `TAX_STATUS`</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>["ACCOUNTS", "BALANCES", "INCOMES", "OWNERS", "RECURRING_EXPENSES", "RISK_INSIGHTS", "TRANSACTIONS"]</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>array</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>integration_type</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>O tipo de tecnologia usada para acessar a instituição. Retornamos um dos seguintes valores:
 - `credentials`: Usa a tecnologia de scraping da Belvo, combinada com credenciais do usuário, para realizar solicitações.
 - `openfinance`: Usa a API de open finance do banco para realizar solicitações.</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>credentials</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>credentials, openfinance</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Indica se a integração da Belvo com a instituição está atualmente ativa (`healthy`) ou em manutenção (`down`).</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>healthy</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1548,7 +1540,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>healthy, down</t>
+          <t>credentials, openfinance</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1556,18 +1548,22 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>openbanking_information</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Informações sobre a instituição no ambiente Open Finance.</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr"/>
+          <t>Indica se a integração da Belvo com a instituição está atualmente ativa (`healthy`) ou em manutenção (`down`).</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1578,31 +1574,31 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>healthy, down</t>
+        </is>
+      </c>
       <c r="I31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>openbanking_information.description</t>
+          <t>openbanking_information</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Uma breve descrição da instituição no ambiente Open Finance. Extraído da lista de instituições regulamentadas pelo Open Finance.</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>A 1ss Bank é uma fintech fundada em janeiro de 2020, com a missão de ajudar empresas com grandes ecossistemas a se tornarem fintechs, integrando e automatizando seus processos financeiros através de APIs e plataforma white-label.</t>
-        </is>
-      </c>
+          <t>Informações sobre a instituição no ambiente Open Finance.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>object</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1622,22 +1618,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>openbanking_information.participants</t>
+          <t>openbanking_information.description</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Lista de servidores de marcas disponíveis pela instituição no Open Finance. Extraído da lista de instituições reguladas pelo Open Finance.</t>
+          <t>Uma breve descrição da instituição no ambiente Open Finance. Extraído da lista de instituições regulamentadas pelo Open Finance.</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>["1ss Bank"]</t>
+          <t>A 1ss Bank é uma fintech fundada em janeiro de 2020, com a missão de ajudar empresas com grandes ecossistemas a se tornarem fintechs, integrando e automatizando seus processos financeiros através de APIs e plataforma white-label.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1657,29 +1653,25 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>openbanking_information.authorization_server_id</t>
+          <t>openbanking_information.participants</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>O ID do servidor de autorização (UUID) da instituição no Ambiente de Open Finance.</t>
+          <t>Lista de servidores de marcas disponíveis pela instituição no Open Finance. Extraído da lista de instituições reguladas pelo Open Finance.</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>aa18fcd3-2f0b-40b1-87db-8930b10b78b1</t>
+          <t>["1ss Bank"]</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -1692,6 +1684,45 @@
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>openbanking_information.authorization_server_id</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>O ID do servidor de autorização (UUID) da instituição no Ambiente de Open Finance.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>aa18fcd3-2f0b-40b1-87db-8930b10b78b1</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -47565,7 +47596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -47777,17 +47808,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>expired_at</t>
+          <t>institution_display_name</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>O timestamp ISO-8601 quando o consentimento irá expirar. No caso de `undefined_consent_expiration` ser `true`, este campo será `null`.</t>
+          <t>O nome de exibição da instituição bancária à qual o consentimento está relacionado.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2021-02-27T13:01:41.941Z</t>
+          <t>Mock Bank</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -47795,11 +47826,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -47816,22 +47843,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>undefined_consent_expiration</t>
+          <t>institution_icon_logo</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Indique se o consentimento é por um período indefinido, ou seja, se não há expiração para o consentimento.</t>
+          <t>A URL para o logotipo da instituição bancária.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>https://assets.belvo.io/institutions/mockbank/logo.svg</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -47851,17 +47878,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>belvo_organization_name</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>O carimbo de data e hora ISO-8601 de quando o ponto de dados foi criado no banco de dados da Belvo.</t>
+          <t>O nome registrado no Belvo da organização que criou o link.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2022-02-09T08:45:50.406032Z</t>
+          <t>ACME Corporation</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -47869,11 +47896,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -47890,10 +47913,237 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>link_id</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>O ID do link Belvo ao qual o consentimento pertence.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2e5d2c5e-6b3a-4b5c-8d1e-9f0a1b2c3d4e</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>user_name</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>O nome fornecido em `consent.identification_info.name` durante a solicitação inicial do Widget Access Token.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Jack White</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>expired_at</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>O timestamp ISO-8601 quando o consentimento irá expirar. No caso de `undefined_consent_expiration` ser `true`, este campo será `null`.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2021-02-27T13:01:41.941Z</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>undefined_consent_expiration</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Indique se o consentimento é por um período indefinido, ou seja, se não há expiração para o consentimento.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>consent_duration</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>A duração do consentimento em dias. No caso de `undefined_consent_expiration` ser `true`, este campo será `null`.
+Valores possíveis:
+- `92` (3 meses)
+- `183` (6 meses)
+- `275` (9 meses)
+- `366` (12 meses)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>O carimbo de data e hora ISO-8601 de quando o ponto de dados foi criado no banco de dados da Belvo.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-09T08:45:50.406032Z</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>O status do consentimento na rede de open finance. Pode ser:
   - `AUTHORISED`: O consentimento ainda é válido para uso até a data de `expired_at`.
@@ -47904,224 +48154,14 @@
   - `null`</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>AUTHORISED</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>AUTHORISED, AWAITING_AUTHORISATION_CONFIRMATION, AWAITING_AUTHORISATION, REJECTED, EXPIRED, None</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>permissions</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Detalhes sobre as permissões associadas ao consentimento.</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>permissions.ACCOUNTS</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Uma lista de permissões de open banking relacionadas ao acesso a informações de conta.</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>["ACCOUNTS_OVERDRAFT_LIMITS_READ", "ACCOUNTS_READ", "ACCOUNTS_TRANSACTIONS_READ", "ACCOUNTS_BALANCES_READ"]</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>permissions.CREDIT_CARDS</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Uma lista de permissões de open banking relacionadas ao acesso a informações de cartão de crédito.</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>["CREDIT_CARDS_ACCOUNTS_LIMITS_READ", "CREDIT_CARDS_ACCOUNTS_BILLS_READ", "CREDIT_CARDS_ACCOUNTS_TRANSACTIONS_READ", "CREDIT_CARDS_ACCOUNTS_BILLS_TRANSACTIONS_READ", "CREDIT_CARDS_ACCOUNTS_READ"]</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>permissions.CREDIT_OPERATIONS</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Uma lista de permissões de open banking relacionadas ao acesso a informações de produtos de crédito.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>["LOANS_READ", "LOANS_WARRANTIES_READ", "LOANS_SCHEDULED_INSTALMENTS_READ", "LOANS_PAYMENTS_READ", "FINANCINGS_READ", "FINANCINGS_WARRANTIES_READ", "FINANCINGS_SCHEDULED_INSTALMENTS_READ", "FINANCINGS_PAYMENTS_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_WARRANTIES_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_SCHEDULED_INSTALMENTS_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_PAYMENTS_READ", "INVOICE_FINANCINGS_READ", "INVOICE_FINANCINGS_WARRANTIES_READ", "INVOICE_FINANCINGS_SCHEDULED_INSTALMENTS_READ", "INVOICE_FINANCINGS_PAYMENTS_READ"]</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>permissions.REGISTER</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Uma lista de permissões de open banking relacionadas ao acesso a informações pessoais.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>["CUSTOMERS_PERSONAL_IDENTIFICATIONS_READ", "CUSTOMERS_PERSONAL_ADITTIONALINFO_READ"]</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>permissions.RESOURCES</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Uma lista de permissões funcionais necessárias para interagir com as permissões.</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>["RESOURCES_READ"]</t>
-        </is>
-      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -48132,11 +48172,256 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>AUTHORISED, AWAITING_AUTHORISATION_CONFIRMATION, AWAITING_AUTHORISATION, REJECTED, EXPIRED, None</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>permissions</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Detalhes sobre as permissões associadas ao consentimento.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>permissions.ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Uma lista de permissões de open banking relacionadas ao acesso a informações de conta.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>["ACCOUNTS_OVERDRAFT_LIMITS_READ", "ACCOUNTS_READ", "ACCOUNTS_TRANSACTIONS_READ", "ACCOUNTS_BALANCES_READ"]</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>permissions.CREDIT_CARDS</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Uma lista de permissões de open banking relacionadas ao acesso a informações de cartão de crédito.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>["CREDIT_CARDS_ACCOUNTS_LIMITS_READ", "CREDIT_CARDS_ACCOUNTS_BILLS_READ", "CREDIT_CARDS_ACCOUNTS_TRANSACTIONS_READ", "CREDIT_CARDS_ACCOUNTS_BILLS_TRANSACTIONS_READ", "CREDIT_CARDS_ACCOUNTS_READ"]</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>permissions.CREDIT_OPERATIONS</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Uma lista de permissões de open banking relacionadas ao acesso a informações de produtos de crédito.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>["LOANS_READ", "LOANS_WARRANTIES_READ", "LOANS_SCHEDULED_INSTALMENTS_READ", "LOANS_PAYMENTS_READ", "FINANCINGS_READ", "FINANCINGS_WARRANTIES_READ", "FINANCINGS_SCHEDULED_INSTALMENTS_READ", "FINANCINGS_PAYMENTS_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_WARRANTIES_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_SCHEDULED_INSTALMENTS_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_PAYMENTS_READ", "INVOICE_FINANCINGS_READ", "INVOICE_FINANCINGS_WARRANTIES_READ", "INVOICE_FINANCINGS_SCHEDULED_INSTALMENTS_READ", "INVOICE_FINANCINGS_PAYMENTS_READ"]</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>permissions.REGISTER</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Uma lista de permissões de open banking relacionadas ao acesso a informações pessoais.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>["CUSTOMERS_PERSONAL_IDENTIFICATIONS_READ", "CUSTOMERS_PERSONAL_ADITTIONALINFO_READ"]</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>permissions.RESOURCES</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Uma lista de permissões funcionais necessárias para interagir com as permissões.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>["RESOURCES_READ"]</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>permissions.INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Uma lista de permissões de open banking relacionadas ao acesso a informações de investimentos.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>["BANK_FIXED_INCOMES_READ", "CREDIT_FIXED_INCOMES_READ", "FUNDS_READ", "VARIABLE_INCOMES_READ", "TREASURE_TITLES_READ"]</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data_dictionaries/pt-BR/Belvo_Data_Dictionary_pt-BR.xlsx
+++ b/data_dictionaries/pt-BR/Belvo_Data_Dictionary_pt-BR.xlsx
@@ -11259,7 +11259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -11518,22 +11518,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>internal_identification</t>
+          <t>days_since_extraction</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ID único para o usuário de acordo com a instituição. Para IMSS e ISSSTE México, este é o CURP.</t>
+          <t>O número de dias que se passaram desde que os dados de emprego foram originalmente extraídos da instituição.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>BLPM951331IONVGR54</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -11553,18 +11553,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>personal_data</t>
+          <t>internal_identification</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Detalhes sobre as informações pessoais do indivíduo.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
+          <t>ID único para o usuário de acordo com a instituição. Para IMSS e ISSSTE México, este é o CURP.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>BLPM951331IONVGR54</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -11584,22 +11588,18 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>personal_data.official_name</t>
+          <t>personal_data</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>O nome legal do indivíduo.</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Bruce Banner del Torro</t>
-        </is>
-      </c>
+          <t>Detalhes sobre as informações pessoais do indivíduo.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>object</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -11619,17 +11619,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>personal_data.first_name</t>
+          <t>personal_data.official_name</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>O primeiro nome do indivíduo.</t>
+          <t>O nome legal do indivíduo.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Bruce</t>
+          <t>Bruce Banner del Torro</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -11654,17 +11654,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>personal_data.last_name</t>
+          <t>personal_data.first_name</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>O sobrenome do indivíduo.</t>
+          <t>O primeiro nome do indivíduo.</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Banner del Torro</t>
+          <t>Bruce</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -11689,17 +11689,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>personal_data.birth_date</t>
+          <t>personal_data.last_name</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>A data de nascimento do indivíduo, no formato `YYYY-MM-DD`.</t>
+          <t>O sobrenome do indivíduo.</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2022-02-09</t>
+          <t>Banner del Torro</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -11707,11 +11707,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -11728,21 +11724,29 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>personal_data.entitlements</t>
+          <t>personal_data.birth_date</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Detalhes sobre os benefícios aos quais o indivíduo tem direito.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
+          <t>A data de nascimento do indivíduo, no formato `YYYY-MM-DD`.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-09</t>
+        </is>
+      </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -11750,7 +11754,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -11759,22 +11763,18 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>personal_data.entitlements.entitled_to_health_insurance</t>
+          <t>personal_data.entitlements</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Indica se o indivíduo tem ou não direito a seguro de saúde.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>Detalhes sobre os benefícios aos quais o indivíduo tem direito.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>object</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -11794,12 +11794,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>personal_data.entitlements.entitled_to_company_benefits</t>
+          <t>personal_data.entitlements.entitled_to_health_insurance</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Indica se o indivíduo tem ou não direito aos benefícios da empresa.</t>
+          <t>Indica se o indivíduo tem ou não direito a seguro de saúde.</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -11829,25 +11829,25 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>personal_data.entitlements.valid_until</t>
+          <t>personal_data.entitlements.entitled_to_company_benefits</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Data até quando o indivíduo está coberto pelo seguro de saúde e/ou benefícios da empresa. Se for `null`, o funcionário está atualmente trabalhando e não é necessária uma data de término.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
+          <t>Indica se o indivíduo tem ou não direito aos benefícios da empresa.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -11864,10 +11864,45 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>personal_data.entitlements.valid_until</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Data até quando o indivíduo está coberto pelo seguro de saúde e/ou benefícios da empresa. Se for `null`, o funcionário está atualmente trabalhando e não é necessária uma data de término.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>personal_data.entitlements.status</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Indica o status de emprego do indivíduo. Retornamos uma das seguintes respostas:
 - `EMPLOYED`
@@ -11876,49 +11911,14 @@
 - `null`</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>EMPLOYED</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>EMPLOYED, RETIRED, UNEMPLOYED, null</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>personal_data.document_ids</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Detalhes sobre os documentos de identificação do indivíduo.</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -11932,16 +11932,51 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>EMPLOYED, RETIRED, UNEMPLOYED, null</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>personal_data.document_ids</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Detalhes sobre os documentos de identificação do indivíduo.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>personal_data.document_ids[].document_type</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>O tipo de documento relacionado ao indivíduo. Retornamos um dos seguintes valores:
   - `NSS`
@@ -11949,48 +11984,9 @@
   - `RFC`</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>NSS</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>NSS, CURP, RFC</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>personal_data.document_ids[].document_number</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>O número do documento de identidade (como uma string).</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>10277663582</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -12009,23 +12005,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>NSS, CURP, RFC</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>personal_data.email</t>
+          <t>personal_data.document_ids[].document_number</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>O endereço de e-mail do indivíduo.</t>
+          <t>O número do documento de identidade (como uma string).</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>bruce.banner@avengers.com</t>
+          <t>10277663582</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -12050,61 +12050,57 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>personal_data.email</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>O endereço de e-mail do indivíduo.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>bruce.banner@avengers.com</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>social_security_summary</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Detalhes sobre as contribuições previdenciárias do indivíduo, de acordo com o IMSS.
 &gt;**Nota**: Para o ISSSTE México, este valor retornará `null`.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>social_security_summary.weeks_redeemed</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Número de semanas que o indivíduo precisou retirar de sua aposentadoria.</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12121,12 +12117,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>social_security_summary.weeks_reinstated</t>
+          <t>social_security_summary.weeks_redeemed</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Número de semanas que o indivíduo contribuiu novamente para o seu fundo de pensão (*AFORE*), após tê-lo resgatado anteriormente.</t>
+          <t>Número de semanas que o indivíduo precisou retirar de sua aposentadoria.</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -12160,17 +12156,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>social_security_summary.weeks_contributed</t>
+          <t>social_security_summary.weeks_reinstated</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Número de semanas que o indivíduo contribuiu para a sua previdência social, com base no número de semanas que o indivíduo trabalhou de acordo com o IMSS.</t>
+          <t>Número de semanas que o indivíduo contribuiu novamente para o seu fundo de pensão (*AFORE*), após tê-lo resgatado anteriormente.</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -12199,21 +12195,29 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>employment_records</t>
+          <t>social_security_summary.weeks_contributed</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Detalhes sobre o histórico de emprego do indivíduo.</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr"/>
+          <t>Número de semanas que o indivíduo contribuiu para a sua previdência social, com base no número de semanas que o indivíduo trabalhou de acordo com o IMSS.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12221,7 +12225,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -12230,29 +12234,21 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>employment_records[].collected_at</t>
+          <t>employment_records</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>O carimbo de data/hora ISO-8601 quando o ponto de dados foi coletado.</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>2020-04-23T21:32:55.336854+00:00</t>
-        </is>
-      </c>
+          <t>Detalhes sobre o histórico de emprego do indivíduo.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12269,101 +12265,101 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>employment_records[].collected_at</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>O carimbo de data/hora ISO-8601 quando o ponto de dados foi coletado.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2020-04-23T21:32:55.336854+00:00</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>employment_records[].employer</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>O nome oficial do empregador.
 &gt;**Nota**: Para o ISSSTE México, este é o nome oficial da entidade junto com a entidade responsável por gerenciar as informações do empregado, separados por um ponto e vírgula (`;`). Por exemplo: SECRETARIA DE EDUCACION PUBLICA (SEP);SECRETARIA DE EDUCACION PUBLICA (SEP).</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Batman Enterprises CDMX</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>employment_records[].employer_id</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>O ID oficial do empregador, de acordo com o país.
 &gt;**Nota**: Para ISSSTE México, este valor retornará `null`.</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>780-BAT-88769-CDMX</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>employment_records[].start_date</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Data de início do emprego, no formato `YYYY-MM-DD`.</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>2019-10-10</t>
-        </is>
-      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12371,7 +12367,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -12380,69 +12376,69 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>employment_records[].start_date</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Data de início do emprego, no formato `YYYY-MM-DD`.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>2019-10-10</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>employment_records[].end_date</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Data de término do emprego, no formato `YYYY-MM-DD`.
 &gt;**Nota**: Este campo retornará `null` para o emprego atual do usuário.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>2019-12-31</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>employment_records[].weeks_employed</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Número de semanas em que o indivíduo esteve empregado.</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12450,7 +12446,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -12459,143 +12455,147 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>employment_records[].weeks_employed</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Número de semanas em que o indivíduo esteve empregado.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>employment_records[].state</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Em que estado geográfico o indivíduo estava empregado, de acordo com o país.
 &gt;**Nota**: Para ISSSTE México, este valor retornará `null`.</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>DISTRITO FEDERAL</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>employment_records[].most_recent_base_salary</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>O salário base mais recente que o indivíduo recebeu.
 - Para o IMSS México, esse valor é calculado incluindo os benefícios aos quais o indivíduo tem direito ao longo do ano.
 - Para o ISSSTE México, esse valor é calculado dividindo o `monthly_salary` por 30 (dias) e exclui os benefícios do indivíduo.</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>762.54</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>employment_records[].monthly_salary</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>O salário mensal do indivíduo, incluindo quaisquer benefícios adicionais.
 - Para o IMSS México, este valor é calculado incluindo os benefícios aos quais o indivíduo tem direito ao longo do ano.
 - Para o ISSSTE México, este valor é calculado excluindo os benefícios.</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>23193.925</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>employment_records[].currency</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>O código de moeda de três letras em que o salário é pago.</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>MXN</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12612,18 +12612,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>employment_records[].employment_status_updates</t>
+          <t>employment_records[].currency</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Detalhes sobre quaisquer mudanças de emprego do indivíduo.</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr"/>
+          <t>O código de moeda de três letras em que o salário é pago.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -12634,7 +12638,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -12643,10 +12647,41 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>employment_records[].employment_status_updates</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Detalhes sobre quaisquer mudanças de emprego do indivíduo.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>employment_records[].employment_status_updates[].event</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Para o IMSS México, este é o evento que causou a mudança no status de emprego ou salário. Retornamos um dos seguintes valores:
 - `DISMISSED_RESIGNED`: O funcionário foi demitido ou pediu demissão.
@@ -12661,99 +12696,60 @@
 - `DYE_CERTIFICATE`: Indica que a informação foi recebida de uma instituição afiliada, **Dependencia y Entidad (DYE)**.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>HIRED</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>DISMISSED_RESIGNED, SALARY_MODIFICATION, HIRED, VOLUNTARY_CONTRIBUTION, ABSENCE, SICK_LEAVE, NORMAL, BDUTA_CERTIFICATE, DYE_CERTIFICATE</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>employment_records[].employment_status_updates[].base_salary</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>O salário base do indivíduo, atualizado na `update_date`.
   - Para o IMSS México, esse valor é calculado incluindo os benefícios aos quais o indivíduo tem direito ao longo do ano.
   - Para o ISSSTE México, esse valor é calculado excluindo os benefícios do indivíduo.</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>1033.09</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>float</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>employment_records[].employment_status_updates[].update_date</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>A data em que o evento de emprego ocorreu, no formato `YYYY-MM-DD`.</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>2021-09-01</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -12772,47 +12768,86 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>employment_records[].employment_status_updates[].update_date</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>A data em que o evento de emprego ocorreu, no formato `YYYY-MM-DD`.</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
           <t>employment_scores</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Um array de pontuações de `employment_record`. Cada pontuação fornece uma visão sobre a empregabilidade e o potencial de geração de renda em um determinado período.
 &gt; **Nota 1**: Este campo está disponível apenas para links criados com o IMSS do México. Para outras instituições, este campo retornará `null`.
 &gt; **Nota 2**: Este campo retornará `null` para registros de emprego recuperados antes de 16-04-2024. Para registros de emprego gerados antes de 16-04-2024, será necessário fazer uma nova solicitação POST para recuperar os registros de emprego e calcular as pontuações.</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>[{"score": 722, "period": 3, "version": "1.0.0"}, {"score": 612, "period": 6, "version": "1.0.0"}, {"score": 570, "period": 12, "version": "1.0.0"}]</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>array</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>employment_scores[].score</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Uma pontuação entre 300 e 900 que fornece uma visão sobre a empregabilidade e o potencial de geração de renda.
 - Uma pontuação baixa (próxima de 300) pode indicar uma empregabilidade e potencial de geração de renda previstos mais baixos, sugerindo possíveis desafios para conseguir emprego ou alcançar níveis de renda mais altos no futuro.
@@ -12820,86 +12855,51 @@
 A pontuação pode retornar `null` se o indivíduo não tiver histórico de emprego.</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>employment_scores[].period</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>O número de meses (no futuro) para os quais a pontuação é calculada.
 Por exemplo, um período de `6` indica que a pontuação é calculada para os próximos `6` meses.
 &gt; **Nota**: Atualmente, a Belvo calcula a pontuação para 3, 6 e 12 meses.</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>integer</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>employment_scores[].version</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>A versão do nosso modelo de pontuação de emprego usada para realizar o cálculo.</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -12919,18 +12919,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>files</t>
+          <t>employment_scores[].version</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Arquivos binários PDF adicionais relacionados ao emprego do indivíduo.</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr"/>
+          <t>A versão do nosso modelo de pontuação de emprego usada para realizar o cálculo.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -12941,7 +12945,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -12950,22 +12954,19 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>files[].type</t>
+          <t>salary_estimation</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>O título do documento.</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>ReporteSemanasCotizadas_190123</t>
-        </is>
-      </c>
+          <t>Fornece uma estimativa modelada do salário base atual do usuário e do status de emprego.
+&gt; **Nota**: Este campo está disponível apenas para links criados com o IMSS do México. Para outras instituições (como ISSSTE), este campo retornará `null`.</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>object</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -12976,7 +12977,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -12985,37 +12986,212 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>salary_estimation.employment_status_estimate</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Status atual de emprego estimado usando um registro de emprego com uma data de relatório passada. Retorna `"EMPLOYED"` (se o `base_salary_estimate` for maior que 0) ou `"UNEMPLOYED"`.</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>EMPLOYED</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>salary_estimation.base_salary_estimate</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Salário base atual (valor diário) estimado usando um registro de emprego com uma data de relatório anterior.</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>salary_estimation.currency</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>O código de moeda de três letras (ISO-4217). Por exemplo, `"MXN"`.</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Arquivos binários PDF adicionais relacionados ao emprego do indivíduo.</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>files[].type</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>O título do documento.</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>ReporteSemanasCotizadas_190123</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
           <t>files[].value</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>O binário PDF do arquivo (como uma string).
 &gt; **Nota**: Em nosso ambiente sandbox, este campo retornará `null`.</t>
         </is>
       </c>
-      <c r="C47" s="2">
+      <c r="C52" s="2">
         <f>PDF_BINARY=</f>
         <v/>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
